--- a/artfynd/A 11826-2025 artfynd.xlsx
+++ b/artfynd/A 11826-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>70845140</v>
+        <v>126404292</v>
       </c>
       <c r="B2" t="n">
-        <v>57280</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56324</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -709,24 +704,19 @@
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>nyligen använt bo</t>
-        </is>
-      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Hagasjön, Vg</t>
+          <t>Sålen, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>346096.7975111857</v>
+        <v>346097</v>
       </c>
       <c r="R2" t="n">
-        <v>6364349.851463132</v>
+        <v>6364350</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,27 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-11-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-07-07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>vide</t>
+          <t>Hasselmusinventering Boris Berglund 2007, Inrapporterad av Marks kommun</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +770,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Boris Berglund</t>
+          <t>Via Jenny Pleym</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 11826-2025 artfynd.xlsx
+++ b/artfynd/A 11826-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126404292</v>
       </c>
       <c r="B2" t="n">
-        <v>56324</v>
+        <v>56325</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
